--- a/web/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -756,7 +756,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -818,7 +818,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14582,7 +14582,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20288,7 +20288,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20350,7 +20350,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20536,7 +20536,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21342,7 +21342,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22396,7 +22396,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22582,7 +22582,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22706,7 +22706,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22768,7 +22768,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22892,7 +22892,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23450,7 +23450,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23698,7 +23698,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23946,7 +23946,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24008,7 +24008,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24380,7 +24380,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25000,7 +25000,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25062,7 +25062,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25186,7 +25186,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25372,7 +25372,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25930,7 +25930,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26612,7 +26612,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27356,7 +27356,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27418,7 +27418,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27480,7 +27480,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27604,7 +27604,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27666,7 +27666,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27790,7 +27790,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28472,7 +28472,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28658,7 +28658,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28906,7 +28906,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -29030,7 +29030,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29216,7 +29216,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29278,7 +29278,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29340,7 +29340,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -29774,7 +29774,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -29836,7 +29836,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -29960,7 +29960,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30084,7 +30084,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30146,7 +30146,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30270,7 +30270,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30332,7 +30332,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30456,7 +30456,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30518,7 +30518,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -30642,7 +30642,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -30766,7 +30766,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -30828,7 +30828,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -30952,7 +30952,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -31014,7 +31014,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -31138,7 +31138,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -31510,7 +31510,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -31634,7 +31634,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -31820,7 +31820,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -31882,7 +31882,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -31944,7 +31944,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -32068,7 +32068,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32130,7 +32130,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -32192,7 +32192,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -32316,7 +32316,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -32440,7 +32440,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -32626,7 +32626,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -32812,7 +32812,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -32936,7 +32936,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -32998,7 +32998,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -33060,7 +33060,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -33246,7 +33246,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -33308,7 +33308,7 @@
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H527" s="5" t="n">
@@ -33370,7 +33370,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -33494,7 +33494,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -33742,7 +33742,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -33866,7 +33866,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -33928,7 +33928,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -34114,7 +34114,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -34238,7 +34238,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -34486,7 +34486,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -34548,7 +34548,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -34610,7 +34610,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -34672,7 +34672,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -34858,7 +34858,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -34920,7 +34920,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -35168,7 +35168,7 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
@@ -35230,7 +35230,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -35292,7 +35292,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -35354,7 +35354,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -35549,7 +35549,7 @@
           <t>A | 1267呎 (4+房)
 $4409万
 $34,800/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -35557,7 +35557,7 @@
           <t>B | 1224呎 (4+房)
 $4198万
 $34,300/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -35565,7 +35565,7 @@
           <t>C | 464呎 (2房)
 $1105万
 $23,812/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -35573,7 +35573,7 @@
           <t>D | 446呎 (2房)
 $1094万
 $24,527/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -35581,7 +35581,7 @@
           <t>E | 474呎 (2房)
 $1133万
 $23,895/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -35589,7 +35589,7 @@
           <t>F | 443呎 (2房)
 $1107万
 $24,980/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -35597,7 +35597,7 @@
           <t>G | 759呎 (3房)
 $1990万
 $26,217/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -35605,7 +35605,7 @@
           <t>H | 718呎 (3房)
 $1848万
 $25,740/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -35613,7 +35613,7 @@
           <t>J | 729呎 (3房)
 $1894万
 $25,988/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -35628,7 +35628,7 @@
           <t>A | 1267呎 (4+房)
 $4308万
 $34,000/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -35636,7 +35636,7 @@
           <t>B | 1224呎 (4+房)
 $3966万
 $32,400/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -35644,7 +35644,7 @@
           <t>C | 464呎 (2房)
 $1069万
 $23,047/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -35652,7 +35652,7 @@
           <t>D | 446呎 (2房)
 $1090万
 $24,430/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -35660,7 +35660,7 @@
           <t>E | 474呎 (2房)
 $1096万
 $23,129/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -35668,7 +35668,7 @@
           <t>F | 443呎 (2房)
 $1099万
 $24,817/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -35676,7 +35676,7 @@
           <t>G | 759呎 (3房)
 $1941万
 $25,569/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -35684,7 +35684,7 @@
           <t>H | 718呎 (3房)
 $1834万
 $25,536/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -35692,7 +35692,7 @@
           <t>J | 729呎 (3房)
 $1848万
 $25,344/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -35707,7 +35707,7 @@
           <t>A | 1267呎 (4+房)
 $4080万
 $32,200/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -35715,7 +35715,7 @@
           <t>B | 1224呎 (4+房)
 $4039万
 $33,000/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -35723,7 +35723,7 @@
           <t>C | 464呎 (2房)
 $1066万
 $22,963/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -35731,7 +35731,7 @@
           <t>D | 446呎 (2房)
 $1085万
 $24,336/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -35739,7 +35739,7 @@
           <t>E | 474呎 (2房)
 $1092万
 $23,042/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -35747,7 +35747,7 @@
           <t>F | 443呎 (2房)
 $1095万
 $24,722/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -35755,7 +35755,7 @@
           <t>G | 759呎 (3房)
 $1932万
 $25,455/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -35763,7 +35763,7 @@
           <t>H | 718呎 (3房)
 $1825万
 $25,421/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -35771,7 +35771,7 @@
           <t>J | 729呎 (3房)
 $1871万
 $25,668/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -35786,7 +35786,7 @@
           <t>A | 1267呎 (4+房)
 $4004万
 $31,600/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -35794,7 +35794,7 @@
           <t>B | 1224呎 (4+房)
 $3819万
 $31,200/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -35802,7 +35802,7 @@
           <t>C | 464呎 (2房)
 $1061万
 $22,873/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -35810,7 +35810,7 @@
           <t>D | 446呎 (2房)
 $1081万
 $24,242/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -35818,7 +35818,7 @@
           <t>E | 474呎 (2房)
 $1088万
 $22,956/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -35826,7 +35826,7 @@
           <t>F | 443呎 (2房)
 $1088万
 $24,571/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -35834,7 +35834,7 @@
           <t>G | 759呎 (3房)
 $1923万
 $25,341/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -35842,7 +35842,7 @@
           <t>H | 718呎 (3房)
 $1817万
 $25,308/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -35850,7 +35850,7 @@
           <t>J | 729呎 (3房)
 $1863万
 $25,551/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -35865,7 +35865,7 @@
           <t>A | 1267呎 (4+房)
 $3915万
 $30,900/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -35873,7 +35873,7 @@
           <t>B | 1224呎 (4+房)
 $3623万
 $29,600/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -35881,7 +35881,7 @@
           <t>C | 464呎 (2房)
 $1057万
 $22,787/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -35889,7 +35889,7 @@
           <t>D | 446呎 (2房)
 $1077万
 $24,150/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -35897,7 +35897,7 @@
           <t>E | 474呎 (2房)
 $1084万
 $22,867/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -35905,7 +35905,7 @@
           <t>F | 443呎 (2房)
 $1084万
 $24,476/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -35913,7 +35913,7 @@
           <t>G | 759呎 (3房)
 $1973万
 $26,000/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -35921,7 +35921,7 @@
           <t>H | 718呎 (3房)
 $1809万
 $25,194/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -35929,7 +35929,7 @@
           <t>J | 729呎 (3房)
 $1854万
 $25,438/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -35944,7 +35944,7 @@
           <t>A | 1267呎 (4+房)
 $3877万
 $30,600/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -35952,7 +35952,7 @@
           <t>B | 1224呎 (4+房)
 $3586万
 $29,300/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -35960,7 +35960,7 @@
           <t>C | 464呎 (2房)
 $1053万
 $22,700/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -35968,7 +35968,7 @@
           <t>D | 446呎 (2房)
 $1073万
 $24,061/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -35976,7 +35976,7 @@
           <t>E | 474呎 (2房)
 $1080万
 $22,783/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -35984,7 +35984,7 @@
           <t>F | 443呎 (2房)
 $1080万
 $24,386/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -35992,7 +35992,7 @@
           <t>G | 759呎 (3房)
 $1906万
 $25,115/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -36000,7 +36000,7 @@
           <t>H | 718呎 (3房)
 $1801万
 $25,081/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -36008,7 +36008,7 @@
           <t>J | 729呎 (3房)
 $1846万
 $25,324/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -36023,7 +36023,7 @@
           <t>A | 1267呎 (4+房)
 $3801万
 $30,000/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -36031,7 +36031,7 @@
           <t>B | 1224呎 (4+房)
 $3623万
 $29,600/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -36039,7 +36039,7 @@
           <t>C | 464呎 (2房)
 $1049万
 $22,614/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -36047,7 +36047,7 @@
           <t>D | 446呎 (2房)
 $1069万
 $23,971/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -36055,7 +36055,7 @@
           <t>E | 474呎 (2房)
 $1076万
 $22,696/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -36063,7 +36063,7 @@
           <t>F | 443呎 (2房)
 $1075万
 $24,269/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -36071,7 +36071,7 @@
           <t>G | 759呎 (3房)
 $1887万
 $24,864/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -36079,7 +36079,7 @@
           <t>H | 718呎 (3房)
 $1783万
 $24,833/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -36087,7 +36087,7 @@
           <t>J | 729呎 (3房)
 $1797万
 $24,649/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -36102,7 +36102,7 @@
           <t>A | 1267呎 (4+房)
 $3788万
 $29,900/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -36110,7 +36110,7 @@
           <t>B | 1224呎 (4+房)
 $3586万
 $29,300/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -36118,7 +36118,7 @@
           <t>C | 464呎 (2房)
 $1076万
 $23,185/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -36126,7 +36126,7 @@
           <t>D | 446呎 (2房)
 $1065万
 $23,879/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -36134,7 +36134,7 @@
           <t>E | 474呎 (2房)
 $1072万
 $22,610/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -36142,7 +36142,7 @@
           <t>F | 443呎 (2房)
 $1071万
 $24,176/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -36150,7 +36150,7 @@
           <t>G | 759呎 (3房)
 $1869万
 $24,621/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -36158,7 +36158,7 @@
           <t>H | 718呎 (3房)
 $1765万
 $24,586/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -36166,7 +36166,7 @@
           <t>J | 729呎 (3房)
 $1779万
 $24,405/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
     </row>
@@ -36181,7 +36181,7 @@
           <t>A | 1267呎 (4+房)
 $3776万
 $29,803/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -36189,7 +36189,7 @@
           <t>B | 1224呎 (4+房)
 $3537万
 $28,900/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -36197,7 +36197,7 @@
           <t>C | 464呎 (2房)
 $1033万
 $22,254/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -36205,7 +36205,7 @@
           <t>D | 446呎 (2房)
 $1071万
 $24,018/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -36213,7 +36213,7 @@
           <t>E | 474呎 (2房)
 $1089万
 $22,981/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -36221,7 +36221,7 @@
           <t>F | 443呎 (2房)
 $1059万
 $23,905/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -36229,7 +36229,7 @@
           <t>G | 759呎 (3房)
 $1891万
 $24,920/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -36237,7 +36237,7 @@
           <t>H | 718呎 (3房)
 $1756万
 $24,464/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -36245,7 +36245,7 @@
           <t>J | 729呎 (3房)
 $1770万
 $24,284/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
     </row>
@@ -36260,7 +36260,7 @@
           <t>A | 1267呎 (4+房)
 $3738万
 $29,500/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -36268,7 +36268,7 @@
           <t>B | 1224呎 (4+房)
 $3476万
 $28,400/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -36276,7 +36276,7 @@
           <t>C | 464呎 (2房)
 $1020万
 $21,978/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -36284,7 +36284,7 @@
           <t>D | 446呎 (2房)
 $1042万
 $23,374/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -36292,7 +36292,7 @@
           <t>E | 474呎 (2房)
 $1046万
 $22,059/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -36300,7 +36300,7 @@
           <t>F | 443呎 (2房)
 $1048万
 $23,666/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -36308,7 +36308,7 @@
           <t>G | 759呎 (3房)
 $1850万
 $24,375/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -36316,7 +36316,7 @@
           <t>H | 718呎 (3房)
 $1748万
 $24,343/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -36324,7 +36324,7 @@
           <t>J | 729呎 (3房)
 $1761万
 $24,162/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -36339,7 +36339,7 @@
           <t>A | 1267呎 (4+房)
 $3712万
 $29,300/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -36347,7 +36347,7 @@
           <t>B | 1224呎 (4+房)
 $3476万
 $28,400/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -36355,7 +36355,7 @@
           <t>C | 464呎 (2房)
 $1044万
 $22,498/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -36363,7 +36363,7 @@
           <t>D | 446呎 (2房)
 $1037万
 $23,247/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -36371,7 +36371,7 @@
           <t>E | 474呎 (2房)
 $1040万
 $21,935/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -36379,7 +36379,7 @@
           <t>F | 443呎 (2房)
 $1042万
 $23,533/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -36387,7 +36387,7 @@
           <t>G | 759呎 (3房)
 $1872万
 $24,661/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -36395,7 +36395,7 @@
           <t>H | 718呎 (3房)
 $1738万
 $24,209/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -36403,7 +36403,7 @@
           <t>J | 729呎 (3房)
 $1752万
 $24,029/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -36418,7 +36418,7 @@
           <t>A | 1267呎 (4+房)
 $3687万
 $29,100/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -36426,7 +36426,7 @@
           <t>B | 1224呎 (4+房)
 $3488万
 $28,500/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -36434,7 +36434,7 @@
           <t>C | 464呎 (2房)
 $1009万
 $21,739/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -36442,7 +36442,7 @@
           <t>D | 446呎 (2房)
 $1019万
 $22,854/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -36450,7 +36450,7 @@
           <t>E | 474呎 (2房)
 $1034万
 $21,819/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -36458,7 +36458,7 @@
           <t>F | 443呎 (2房)
 $1037万
 $23,409/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -36466,7 +36466,7 @@
           <t>G | 759呎 (3房)
 $1830万
 $24,111/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -36474,7 +36474,7 @@
           <t>H | 718呎 (3房)
 $1700万
 $23,670/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -36482,7 +36482,7 @@
           <t>J | 729呎 (3房)
 $1749万
 $23,995/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -36497,7 +36497,7 @@
           <t>A | 1267呎 (4+房)
 $3662万
 $28,900/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -36505,7 +36505,7 @@
           <t>B | 1224呎 (4+房)
 $3403万
 $27,800/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -36513,7 +36513,7 @@
           <t>C | 464呎 (2房)
 $1032万
 $22,250/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -36521,7 +36521,7 @@
           <t>D | 446呎 (2房)
 $1026万
 $22,996/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -36529,7 +36529,7 @@
           <t>E | 474呎 (2房)
 $1028万
 $21,698/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -36537,7 +36537,7 @@
           <t>F | 443呎 (2房)
 $1031万
 $23,278/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -36545,7 +36545,7 @@
           <t>G | 759呎 (3房)
 $1851万
 $24,390/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -36553,7 +36553,7 @@
           <t>H | 718呎 (3房)
 $1719万
 $23,946/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -36561,7 +36561,7 @@
           <t>J | 729呎 (3房)
 $1740万
 $23,863/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -36576,7 +36576,7 @@
           <t>A | 1267呎 (4+房)
 $3624万
 $28,600/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -36584,7 +36584,7 @@
           <t>B | 1224呎 (4+房)
 $3403万
 $27,800/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -36592,7 +36592,7 @@
           <t>C | 464呎 (2房)
 $1026万
 $22,108/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -36600,7 +36600,7 @@
           <t>D | 446呎 (2房)
 $1020万
 $22,868/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -36608,7 +36608,7 @@
           <t>E | 474呎 (2房)
 $1022万
 $21,559/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -36616,7 +36616,7 @@
           <t>F | 443呎 (2房)
 $1026万
 $23,151/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -36624,7 +36624,7 @@
           <t>G | 759呎 (3房)
 $1810万
 $23,846/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -36632,7 +36632,7 @@
           <t>H | 718呎 (3房)
 $1710万
 $23,813/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -36640,7 +36640,7 @@
           <t>J | 729呎 (3房)
 $1730万
 $23,731/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -36655,7 +36655,7 @@
           <t>A | 1267呎 (4+房)
 $3598万
 $28,400/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -36663,7 +36663,7 @@
           <t>B | 1224呎 (4+房)
 $3342万
 $27,304/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -36671,7 +36671,7 @@
           <t>C | 464呎 (2房)
 $1020万
 $21,985/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -36679,7 +36679,7 @@
           <t>D | 446呎 (2房)
 $1014万
 $22,742/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -36687,7 +36687,7 @@
           <t>E | 474呎 (2房)
 $1016万
 $21,441/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -36695,7 +36695,7 @@
           <t>F | 443呎 (2房)
 $1020万
 $23,025/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -36703,7 +36703,7 @@
           <t>G | 759呎 (3房)
 $1800万
 $23,715/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -36711,7 +36711,7 @@
           <t>H | 718呎 (3房)
 $1672万
 $23,283/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -36719,7 +36719,7 @@
           <t>J | 729呎 (3房)
 $1720万
 $23,601/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -36730,85 +36730,6 @@
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 1267呎 (4+房)
-$3573万
-$28,200/呎
-(26年-01月-28日)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 1224呎 (4+房)
-$3366万
-$27,500/呎
-(26年-01月-25日)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 464呎 (2房)
-$1015万
-$21,866/呎
-(24年-12月-19日)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 446呎 (2房)
-$1009万
-$22,621/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 474呎 (2房)
-$1011万
-$21,325/呎
-(25年-03月-06日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 443呎 (2房)
-$1014万
-$22,898/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>G | 759呎 (3房)
-$1790万
-$23,586/呎
-(25年-09月-18日)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>H | 718呎 (3房)
-$1663万
-$23,156/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>J | 729呎 (3房)
-$1663万
-$22,809/呎
-(25年-01月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
 $3573万
@@ -36816,12 +36737,91 @@
 (26年-01月-29日)</t>
         </is>
       </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1224呎 (4+房)
+$3366万
+$27,500/呎
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 464呎 (2房)
+$1015万
+$21,866/呎
+(24年-12月-20日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 446呎 (2房)
+$1009万
+$22,621/呎
+(25年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 474呎 (2房)
+$1011万
+$21,325/呎
+(25年-03月-07日)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 443呎 (2房)
+$1014万
+$22,898/呎
+(25年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 759呎 (3房)
+$1790万
+$23,586/呎
+(25年-09月-19日)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 718呎 (3房)
+$1663万
+$23,156/呎
+(25年-09月-17日)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 729呎 (3房)
+$1663万
+$22,809/呎
+(25年-01月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1267呎 (4+房)
+$3573万
+$28,200/呎
+(26年-01月-30日)</t>
+        </is>
+      </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
 $3360万
 $27,450/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -36829,7 +36829,7 @@
           <t>C | 464呎 (2房)
 $1009万
 $21,746/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -36837,7 +36837,7 @@
           <t>D | 446呎 (2房)
 $1003万
 $22,496/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -36845,7 +36845,7 @@
           <t>E | 474呎 (2房)
 $1005万
 $21,207/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -36853,7 +36853,7 @@
           <t>F | 443呎 (2房)
 $1009万
 $22,774/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -36861,7 +36861,7 @@
           <t>G | 759呎 (3房)
 $1780万
 $23,457/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -36869,7 +36869,7 @@
           <t>H | 718呎 (3房)
 $1653万
 $23,028/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -36877,7 +36877,7 @@
           <t>J | 729呎 (3房)
 $1654万
 $22,684/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -36892,7 +36892,7 @@
           <t>A | 1267呎 (4+房)
 $3560万
 $28,100/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -36900,7 +36900,7 @@
           <t>B | 1224呎 (4+房)
 $3354万
 $27,400/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -36908,7 +36908,7 @@
           <t>C | 464呎 (2房)
 $975万
 $21,017/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -36916,7 +36916,7 @@
           <t>D | 446呎 (2房)
 $998万
 $22,372/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -36924,7 +36924,7 @@
           <t>E | 474呎 (2房)
 $1000万
 $21,093/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -36932,7 +36932,7 @@
           <t>F | 443呎 (2房)
 $1003万
 $22,650/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -36940,7 +36940,7 @@
           <t>G | 759呎 (3房)
 $1771万
 $23,329/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -36948,7 +36948,7 @@
           <t>H | 718呎 (3房)
 $1673万
 $23,297/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -36956,7 +36956,7 @@
           <t>J | 729呎 (3房)
 $1666万
 $22,857/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -36971,7 +36971,7 @@
           <t>A | 1267呎 (4+房)
 $3548万
 $28,000/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -36979,7 +36979,7 @@
           <t>B | 1224呎 (4+房)
 $3342万
 $27,300/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -36987,7 +36987,7 @@
           <t>C | 464呎 (2房)
 $989万
 $21,319/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -36995,7 +36995,7 @@
           <t>D | 446呎 (2房)
 $985万
 $22,085/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -37003,7 +37003,7 @@
           <t>E | 474呎 (2房)
 $986万
 $20,791/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -37011,7 +37011,7 @@
           <t>F | 443呎 (2房)
 $990万
 $22,359/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -37019,7 +37019,7 @@
           <t>G | 759呎 (3房)
 $1761万
 $23,202/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -37027,7 +37027,7 @@
           <t>H | 718呎 (3房)
 $1664万
 $23,170/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -37035,7 +37035,7 @@
           <t>J | 729呎 (3房)
 $1657万
 $22,734/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -37050,7 +37050,7 @@
           <t>A | 1267呎 (4+房)
 $3548万
 $28,000/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -37058,7 +37058,7 @@
           <t>B | 1224呎 (4+房)
 $3525万
 $28,800/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -37066,7 +37066,7 @@
           <t>C | 464呎 (2房)
 $958万
 $20,644/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -37074,7 +37074,7 @@
           <t>D | 446呎 (2房)
 $982万
 $22,007/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -37082,7 +37082,7 @@
           <t>E | 474呎 (2房)
 $1011万
 $21,321/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -37090,7 +37090,7 @@
           <t>F | 443呎 (2房)
 $987万
 $22,280/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -37098,7 +37098,7 @@
           <t>G | 759呎 (3房)
 $1753万
 $23,097/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -37106,7 +37106,7 @@
           <t>H | 718呎 (3房)
 $1628万
 $22,674/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -37114,7 +37114,7 @@
           <t>J | 729呎 (3房)
 $1669万
 $22,894/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -37129,7 +37129,7 @@
           <t>A | 1267呎 (4+房)
 $3636万
 $28,700/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -37137,7 +37137,7 @@
           <t>B | 1224呎 (4+房)
 $3427万
 $28,000/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -37145,7 +37145,7 @@
           <t>C | 464呎 (2房)
 $960万
 $20,692/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -37153,7 +37153,7 @@
           <t>D | 446呎 (2房)
 $995万
 $22,307/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -37161,7 +37161,7 @@
           <t>E | 474呎 (2房)
 $1007万
 $21,247/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -37169,7 +37169,7 @@
           <t>F | 443呎 (2房)
 $984万
 $22,203/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -37177,7 +37177,7 @@
           <t>G | 759呎 (3房)
 $1745万
 $22,995/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -37185,7 +37185,7 @@
           <t>H | 718呎 (3房)
 $1621万
 $22,572/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -37193,7 +37193,7 @@
           <t>J | 729呎 (3房)
 $1668万
 $22,882/呎
-(25年-01月-20日)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -37208,7 +37208,7 @@
           <t>A | 1267呎 (4+房)
 $3535万
 $27,900/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -37216,7 +37216,7 @@
           <t>B | 1224呎 (4+房)
 $3513万
 $28,700/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -37224,7 +37224,7 @@
           <t>C | 464呎 (2房)
 $979万
 $21,097/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -37232,7 +37232,7 @@
           <t>D | 446呎 (2房)
 $975万
 $21,854/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -37240,7 +37240,7 @@
           <t>E | 474呎 (2房)
 $988万
 $20,846/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -37248,7 +37248,7 @@
           <t>F | 443呎 (2房)
 $980万
 $22,126/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -37256,7 +37256,7 @@
           <t>G | 759呎 (3房)
 $1738万
 $22,892/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -37264,7 +37264,7 @@
           <t>H | 718呎 (3房)
 $1613万
 $22,471/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -37272,7 +37272,7 @@
           <t>J | 729呎 (3房)
 $1614万
 $22,137/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
     </row>
@@ -37287,7 +37287,7 @@
           <t>A | 1267呎 (4+房)
 $3535万
 $27,900/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -37295,7 +37295,7 @@
           <t>B | 1224呎 (4+房)
 $3513万
 $28,700/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -37303,7 +37303,7 @@
           <t>C | 464呎 (2房)
 $947万
 $20,418/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -37311,7 +37311,7 @@
           <t>D | 446呎 (2房)
 $971万
 $21,769/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -37319,7 +37319,7 @@
           <t>E | 474呎 (2房)
 $996万
 $21,002/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -37327,7 +37327,7 @@
           <t>F | 443呎 (2房)
 $976万
 $22,038/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -37335,7 +37335,7 @@
           <t>G | 759呎 (3房)
 $1730万
 $22,789/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -37343,7 +37343,7 @@
           <t>H | 718呎 (3房)
 $1606万
 $22,370/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -37351,7 +37351,7 @@
           <t>J | 729呎 (3房)
 $1628万
 $22,329/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -37366,7 +37366,7 @@
           <t>A | 1267呎 (4+房)
 $4004万
 $31,600/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -37374,7 +37374,7 @@
           <t>B | 1224呎 (4+房)
 $3501万
 $28,600/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -37382,7 +37382,7 @@
           <t>C | 464呎 (2房)
 $944万
 $20,347/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -37390,7 +37390,7 @@
           <t>D | 446呎 (2房)
 $968万
 $21,693/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -37398,7 +37398,7 @@
           <t>E | 474呎 (2房)
 $992万
 $20,930/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -37406,7 +37406,7 @@
           <t>F | 443呎 (2房)
 $973万
 $21,962/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -37414,7 +37414,7 @@
           <t>G | 759呎 (3房)
 $1722万
 $22,688/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -37422,7 +37422,7 @@
           <t>H | 718呎 (3房)
 $1599万
 $22,270/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -37430,7 +37430,7 @@
           <t>J | 729呎 (3房)
 $1668万
 $22,875/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -37445,7 +37445,7 @@
           <t>A | 1267呎 (4+房)
 $3674万
 $29,000/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -37453,7 +37453,7 @@
           <t>B | 1224呎 (4+房)
 $3501万
 $28,600/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -37461,7 +37461,7 @@
           <t>C | 464呎 (2房)
 $940万
 $20,267/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -37469,7 +37469,7 @@
           <t>D | 446呎 (2房)
 $964万
 $21,605/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -37477,7 +37477,7 @@
           <t>E | 474呎 (2房)
 $988万
 $20,846/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -37485,7 +37485,7 @@
           <t>F | 443呎 (2房)
 $967万
 $21,819/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -37493,7 +37493,7 @@
           <t>G | 759呎 (3房)
 $1714万
 $22,577/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -37501,7 +37501,7 @@
           <t>H | 718呎 (3房)
 $1591万
 $22,162/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -37509,7 +37509,7 @@
           <t>J | 729呎 (3房)
 $1660万
 $22,764/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -37524,7 +37524,7 @@
           <t>A | 1267呎 (4+房)
 $3649万
 $28,800/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -37532,7 +37532,7 @@
           <t>B | 1224呎 (4+房)
 $3501万
 $28,600/呎
-(26年-06月-23日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -37540,7 +37540,7 @@
           <t>C | 464呎 (2房)
 $964万
 $20,772/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -37548,7 +37548,7 @@
           <t>D | 446呎 (2房)
 $960万
 $21,520/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -37556,7 +37556,7 @@
           <t>E | 474呎 (2房)
 $984万
 $20,764/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -37564,7 +37564,7 @@
           <t>F | 443呎 (2房)
 $960万
 $21,682/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -37572,7 +37572,7 @@
           <t>G | 759呎 (3房)
 $1705万
 $22,465/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -37580,7 +37580,7 @@
           <t>H | 718呎 (3房)
 $1583万
 $22,053/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -37588,7 +37588,7 @@
           <t>J | 729呎 (3房)
 $1605万
 $22,012/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -37619,7 +37619,7 @@
           <t>C | 464呎 (2房)
 $960万
 $20,690/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -37627,7 +37627,7 @@
           <t>D | 446呎 (2房)
 $956万
 $21,433/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -37635,7 +37635,7 @@
           <t>E | 474呎 (2房)
 $980万
 $20,681/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -37643,7 +37643,7 @@
           <t>F | 443呎 (2房)
 $954万
 $21,542/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -37651,7 +37651,7 @@
           <t>G | 759呎 (3房)
 $1696万
 $22,349/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -37659,7 +37659,7 @@
           <t>H | 718呎 (3房)
 $1557万
 $21,687/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -37667,7 +37667,7 @@
           <t>J | 729呎 (3房)
 $1621万
 $22,241/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -37698,7 +37698,7 @@
           <t>C | 464呎 (2房)
 $956万
 $20,608/呎
-(25年-01月-19日)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -37706,7 +37706,7 @@
           <t>D | 446呎 (2房)
 $952万
 $21,350/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -37714,7 +37714,7 @@
           <t>E | 474呎 (2房)
 $952万
 $20,095/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -37722,7 +37722,7 @@
           <t>F | 443呎 (2房)
 $948万
 $21,400/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -37730,7 +37730,7 @@
           <t>G | 759呎 (3房)
 $1688万
 $22,233/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -37738,7 +37738,7 @@
           <t>H | 718呎 (3房)
 $1594万
 $22,202/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -37746,7 +37746,7 @@
           <t>J | 729呎 (3房)
 $1613万
 $22,126/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -37777,7 +37777,7 @@
           <t>C | 464呎 (2房)
 $925万
 $19,942/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -37785,7 +37785,7 @@
           <t>D | 446呎 (2房)
 $965万
 $21,628/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -37793,7 +37793,7 @@
           <t>E | 474呎 (2房)
 $961万
 $20,276/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -37801,7 +37801,7 @@
           <t>F | 443呎 (2房)
 $940万
 $21,228/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -37809,7 +37809,7 @@
           <t>G | 759呎 (3房)
 $1679万
 $22,119/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -37817,7 +37817,7 @@
           <t>H | 718呎 (3房)
 $1541万
 $21,462/呎
-(25年-03月-16日)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -37825,7 +37825,7 @@
           <t>J | 729呎 (3房)
 $1605万
 $22,012/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -37856,7 +37856,7 @@
           <t>C | 464呎 (2房)
 $948万
 $20,433/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -37864,7 +37864,7 @@
           <t>D | 446呎 (2房)
 $944万
 $21,170/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -37872,7 +37872,7 @@
           <t>E | 474呎 (2房)
 $968万
 $20,430/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -37880,7 +37880,7 @@
           <t>F | 443呎 (2房)
 $932万
 $21,038/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -37888,7 +37888,7 @@
           <t>G | 759呎 (3房)
 $1646万
 $21,686/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -37896,7 +37896,7 @@
           <t>H | 718呎 (3房)
 $1511万
 $21,042/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -37904,7 +37904,7 @@
           <t>J | 729呎 (3房)
 $1529万
 $20,970/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -37919,7 +37919,7 @@
           <t>A | 1218呎 (4+房)
 $3654万
 $30,000/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -37927,7 +37927,7 @@
           <t>B | 1181呎 (4+房)
 $3531万
 $29,900/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -37935,7 +37935,7 @@
           <t>C | 464呎 (2房)
 $922万
 $19,881/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -37943,7 +37943,7 @@
           <t>D | 446呎 (2房)
 $933万
 $20,919/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -37951,7 +37951,7 @@
           <t>E | 474呎 (2房)
 $957万
 $20,186/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -37959,7 +37959,7 @@
           <t>F | 443呎 (2房)
 $1108万
 $25,000/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -37967,7 +37967,7 @@
           <t>G | 759呎 (3房)
 $1614万
 $21,261/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -37975,7 +37975,7 @@
           <t>H | 718呎 (3房)
 $1557万
 $21,681/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -37983,7 +37983,7 @@
           <t>J | 729呎 (3房)
 $1640万
 $22,497/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -38151,7 +38151,7 @@
           <t>A | 802呎 (3房)
 $1872万
 $23,340/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -38159,7 +38159,7 @@
           <t>B | 781呎 (3房)
 $2016万
 $25,818/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -38167,7 +38167,7 @@
           <t>C | 509呎 (2房)
 $1281万
 $25,169/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -38175,7 +38175,7 @@
           <t>D | 770呎 (3房)
 $1871万
 $24,294/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -38183,7 +38183,7 @@
           <t>E | 474呎 (2房)
 $1151万
 $24,281/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -38191,7 +38191,7 @@
           <t>F | 537呎 (2房)
 $1289万
 $24,009/呎
-(24年-11月-13日)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -38199,7 +38199,7 @@
           <t>G | 485呎 (2房)
 $1098万
 $22,635/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -38207,7 +38207,7 @@
           <t>H | 489呎 (2房)
 $1200万
 $24,540/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -38215,7 +38215,7 @@
           <t>J | 775呎 (3房)
 $1917万
 $24,732/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -38230,7 +38230,7 @@
           <t>A | 802呎 (3房)
 $1857万
 $23,153/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -38238,7 +38238,7 @@
           <t>B | 781呎 (3房)
 $1944万
 $24,890/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -38246,7 +38246,7 @@
           <t>C | 509呎 (2房)
 $1271万
 $24,969/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -38254,7 +38254,7 @@
           <t>D | 770呎 (3房)
 $1856万
 $24,101/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -38262,7 +38262,7 @@
           <t>E | 474呎 (2房)
 $1113万
 $23,477/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -38270,7 +38270,7 @@
           <t>F | 537呎 (2房)
 $1316万
 $24,512/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -38278,7 +38278,7 @@
           <t>G | 485呎 (2房)
 $1048万
 $21,612/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -38286,7 +38286,7 @@
           <t>H | 489呎 (2房)
 $1158万
 $23,681/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -38294,7 +38294,7 @@
           <t>J | 775呎 (3房)
 $1908万
 $24,622/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -38309,7 +38309,7 @@
           <t>A | 802呎 (3房)
 $1848万
 $23,044/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -38317,7 +38317,7 @@
           <t>B | 781呎 (3房)
 $1935万
 $24,772/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -38325,7 +38325,7 @@
           <t>C | 509呎 (2房)
 $1229万
 $24,147/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -38333,7 +38333,7 @@
           <t>D | 770呎 (3房)
 $1847万
 $23,986/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -38341,7 +38341,7 @@
           <t>E | 474呎 (2房)
 $1107万
 $23,361/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -38349,7 +38349,7 @@
           <t>F | 537呎 (2房)
 $1269万
 $23,629/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -38357,7 +38357,7 @@
           <t>G | 485呎 (2房)
 $1043万
 $21,511/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -38365,7 +38365,7 @@
           <t>H | 489呎 (2房)
 $1183万
 $24,196/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -38373,7 +38373,7 @@
           <t>J | 775呎 (3房)
 $1846万
 $23,814/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -38388,7 +38388,7 @@
           <t>A | 802呎 (3房)
 $1839万
 $22,934/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -38396,7 +38396,7 @@
           <t>B | 781呎 (3房)
 $1981万
 $25,369/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -38404,7 +38404,7 @@
           <t>C | 509呎 (2房)
 $1259万
 $24,731/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -38412,7 +38412,7 @@
           <t>D | 770呎 (3房)
 $1838万
 $23,871/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -38420,7 +38420,7 @@
           <t>E | 474呎 (2房)
 $1102万
 $23,245/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -38428,7 +38428,7 @@
           <t>F | 537呎 (2房)
 $1259万
 $23,443/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -38436,7 +38436,7 @@
           <t>G | 485呎 (2房)
 $1068万
 $22,031/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -38444,7 +38444,7 @@
           <t>H | 489呎 (2房)
 $1142万
 $23,350/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -38452,7 +38452,7 @@
           <t>J | 775呎 (3房)
 $1890万
 $24,392/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -38467,7 +38467,7 @@
           <t>A | 802呎 (3房)
 $1884万
 $23,488/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -38475,7 +38475,7 @@
           <t>B | 781呎 (3房)
 $1891万
 $24,215/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -38483,7 +38483,7 @@
           <t>C | 509呎 (2房)
 $1217万
 $23,917/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -38491,7 +38491,7 @@
           <t>D | 770呎 (3房)
 $1829万
 $23,757/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -38499,7 +38499,7 @@
           <t>E | 474呎 (2房)
 $1096万
 $23,129/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -38507,7 +38507,7 @@
           <t>F | 537呎 (2房)
 $1285万
 $23,931/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -38515,7 +38515,7 @@
           <t>G | 485呎 (2房)
 $1064万
 $21,928/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -38523,7 +38523,7 @@
           <t>H | 489呎 (2房)
 $1133万
 $23,176/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -38531,7 +38531,7 @@
           <t>J | 775呎 (3房)
 $1882万
 $24,277/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -38546,7 +38546,7 @@
           <t>A | 802呎 (3房)
 $1822万
 $22,714/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -38554,7 +38554,7 @@
           <t>B | 781呎 (3房)
 $1882万
 $24,099/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -38562,7 +38562,7 @@
           <t>C | 509呎 (2房)
 $1212万
 $23,804/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -38570,7 +38570,7 @@
           <t>D | 770呎 (3房)
 $1820万
 $23,643/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -38578,7 +38578,7 @@
           <t>E | 474呎 (2房)
 $1091万
 $23,015/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -38586,7 +38586,7 @@
           <t>F | 537呎 (2房)
 $1275万
 $23,743/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -38594,7 +38594,7 @@
           <t>G | 485呎 (2房)
 $1029万
 $21,210/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -38602,7 +38602,7 @@
           <t>H | 489呎 (2房)
 $1158万
 $23,675/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -38610,7 +38610,7 @@
           <t>J | 775呎 (3房)
 $1820万
 $23,481/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
           <t>A | 802呎 (3房)
 $1813万
 $22,606/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -38633,7 +38633,7 @@
           <t>B | 781呎 (3房)
 $1928万
 $24,681/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -38641,7 +38641,7 @@
           <t>C | 509呎 (2房)
 $1206万
 $23,690/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -38649,7 +38649,7 @@
           <t>D | 770呎 (3房)
 $1812万
 $23,530/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -38657,7 +38657,7 @@
           <t>E | 474呎 (2房)
 $1086万
 $22,901/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -38665,7 +38665,7 @@
           <t>F | 537呎 (2房)
 $1265万
 $23,553/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -38673,7 +38673,7 @@
           <t>G | 485呎 (2房)
 $1068万
 $22,010/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -38681,7 +38681,7 @@
           <t>H | 489呎 (2房)
 $1149万
 $23,497/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -38689,7 +38689,7 @@
           <t>J | 775呎 (3房)
 $1864万
 $24,050/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -38704,7 +38704,7 @@
           <t>A | 802呎 (3房)
 $1795万
 $22,384/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -38712,7 +38712,7 @@
           <t>B | 781呎 (3房)
 $1855万
 $23,746/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -38720,7 +38720,7 @@
           <t>C | 509呎 (2房)
 $1229万
 $24,138/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -38728,7 +38728,7 @@
           <t>D | 770呎 (3房)
 $1794万
 $23,297/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -38736,7 +38736,7 @@
           <t>E | 474呎 (2房)
 $1078万
 $22,741/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -38744,7 +38744,7 @@
           <t>F | 537呎 (2房)
 $1220万
 $22,728/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -38752,7 +38752,7 @@
           <t>G | 485呎 (2房)
 $1062万
 $21,907/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -38760,7 +38760,7 @@
           <t>H | 489呎 (2房)
 $1109万
 $22,685/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -38768,7 +38768,7 @@
           <t>J | 775呎 (3房)
 $1803万
 $23,261/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -38783,7 +38783,7 @@
           <t>A | 802呎 (3房)
 $1829万
 $22,805/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -38791,7 +38791,7 @@
           <t>B | 781呎 (3房)
 $1836万
 $23,512/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -38799,7 +38799,7 @@
           <t>C | 509呎 (2房)
 $1216万
 $23,898/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -38807,7 +38807,7 @@
           <t>D | 770呎 (3房)
 $1776万
 $23,066/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -38815,7 +38815,7 @@
           <t>E | 474呎 (2房)
 $1070万
 $22,582/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -38823,7 +38823,7 @@
           <t>F | 537呎 (2房)
 $1212万
 $22,570/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -38831,7 +38831,7 @@
           <t>G | 485呎 (2房)
 $1058万
 $21,806/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -38839,7 +38839,7 @@
           <t>H | 489呎 (2房)
 $1134万
 $23,194/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -38847,7 +38847,7 @@
           <t>J | 775呎 (3房)
 $1847万
 $23,827/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -38862,7 +38862,7 @@
           <t>A | 802呎 (3房)
 $1819万
 $22,681/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -38870,7 +38870,7 @@
           <t>B | 781呎 (3房)
 $1826万
 $23,383/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -38878,7 +38878,7 @@
           <t>C | 509呎 (2房)
 $1176万
 $23,094/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -38886,7 +38886,7 @@
           <t>D | 770呎 (3房)
 $1766万
 $22,940/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -38894,7 +38894,7 @@
           <t>E | 474呎 (2房)
 $1064万
 $22,449/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -38902,7 +38902,7 @@
           <t>F | 537呎 (2房)
 $1239万
 $23,065/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -38910,7 +38910,7 @@
           <t>G | 485呎 (2房)
 $1053万
 $21,703/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -38918,7 +38918,7 @@
           <t>H | 489呎 (2房)
 $1127万
 $23,047/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -38926,7 +38926,7 @@
           <t>J | 775呎 (3房)
 $1838万
 $23,715/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -38941,7 +38941,7 @@
           <t>A | 802呎 (3房)
 $1758万
 $21,919/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -38949,7 +38949,7 @@
           <t>B | 781呎 (3房)
 $1869万
 $23,931/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -38957,7 +38957,7 @@
           <t>C | 509呎 (2房)
 $1203万
 $23,639/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -38965,7 +38965,7 @@
           <t>D | 770呎 (3房)
 $1757万
 $22,814/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -38973,7 +38973,7 @@
           <t>E | 474呎 (2房)
 $1088万
 $22,949/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -38981,7 +38981,7 @@
           <t>F | 537呎 (2房)
 $1229万
 $22,894/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -38989,7 +38989,7 @@
           <t>G | 485呎 (2房)
 $1005万
 $20,718/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -38997,7 +38997,7 @@
           <t>H | 489呎 (2房)
 $1119万
 $22,875/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -39005,7 +39005,7 @@
           <t>J | 775呎 (3房)
 $1777万
 $22,930/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -39020,7 +39020,7 @@
           <t>A | 802呎 (3房)
 $1748万
 $21,799/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39028,7 +39028,7 @@
           <t>B | 781呎 (3房)
 $1806万
 $23,128/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39036,7 +39036,7 @@
           <t>C | 509呎 (2房)
 $1196万
 $23,507/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -39044,7 +39044,7 @@
           <t>D | 770呎 (3房)
 $1747万
 $22,690/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -39052,7 +39052,7 @@
           <t>E | 474呎 (2房)
 $1081万
 $22,804/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -39060,7 +39060,7 @@
           <t>F | 537呎 (2房)
 $1222万
 $22,747/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -39068,7 +39068,7 @@
           <t>G | 485呎 (2房)
 $1029万
 $21,221/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -39076,7 +39076,7 @@
           <t>H | 489呎 (2房)
 $1111万
 $22,728/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -39084,7 +39084,7 @@
           <t>J | 775呎 (3房)
 $1820万
 $23,480/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -39099,7 +39099,7 @@
           <t>A | 802呎 (3房)
 $1789万
 $22,310/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39107,7 +39107,7 @@
           <t>B | 781呎 (3房)
 $1796万
 $23,000/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39115,7 +39115,7 @@
           <t>C | 509呎 (2房)
 $1156万
 $22,719/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -39123,7 +39123,7 @@
           <t>D | 770呎 (3房)
 $1738万
 $22,565/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -39131,7 +39131,7 @@
           <t>E | 474呎 (2房)
 $1074万
 $22,656/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -39139,7 +39139,7 @@
           <t>F | 537呎 (2房)
 $1214万
 $22,598/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -39147,7 +39147,7 @@
           <t>G | 485呎 (2房)
 $1038万
 $21,400/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -39155,7 +39155,7 @@
           <t>H | 489呎 (2房)
 $1104万
 $22,579/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -39163,7 +39163,7 @@
           <t>J | 775呎 (3房)
 $1811万
 $23,364/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -39178,7 +39178,7 @@
           <t>A | 802呎 (3房)
 $1780万
 $22,190/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39186,7 +39186,7 @@
           <t>B | 781呎 (3房)
 $1838万
 $23,540/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -39194,7 +39194,7 @@
           <t>C | 509呎 (2房)
 $1150万
 $22,595/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -39202,7 +39202,7 @@
           <t>D | 770呎 (3房)
 $1706万
 $22,149/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -39210,7 +39210,7 @@
           <t>E | 474呎 (2房)
 $1037万
 $21,871/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -39218,7 +39218,7 @@
           <t>F | 537呎 (2房)
 $1206万
 $22,454/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -39226,7 +39226,7 @@
           <t>G | 485呎 (2房)
 $991万
 $20,429/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -39234,7 +39234,7 @@
           <t>H | 489呎 (2房)
 $1097万
 $22,434/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -39242,7 +39242,7 @@
           <t>J | 775呎 (3房)
 $1802万
 $23,246/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
           <t>A | 802呎 (3房)
 $1770万
 $22,067/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -39265,7 +39265,7 @@
           <t>B | 781呎 (3房)
 $1828万
 $23,411/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39273,7 +39273,7 @@
           <t>C | 509呎 (2房)
 $1177万
 $23,126/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -39281,7 +39281,7 @@
           <t>D | 770呎 (3房)
 $1696万
 $22,029/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -39289,7 +39289,7 @@
           <t>E | 474呎 (2房)
 $1060万
 $22,365/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -39297,7 +39297,7 @@
           <t>F | 537呎 (2房)
 $1198万
 $22,307/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -39305,7 +39305,7 @@
           <t>G | 485呎 (2房)
 $1015万
 $20,924/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -39313,7 +39313,7 @@
           <t>H | 489呎 (2房)
 $1059万
 $21,661/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -39321,7 +39321,7 @@
           <t>J | 775呎 (3房)
 $1793万
 $23,132/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -39336,7 +39336,7 @@
           <t>A | 802呎 (3房)
 $1760万
 $21,948/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -39344,7 +39344,7 @@
           <t>B | 781呎 (3房)
 $1767万
 $22,626/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39352,7 +39352,7 @@
           <t>C | 509呎 (2房)
 $1171万
 $22,998/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -39360,7 +39360,7 @@
           <t>D | 770呎 (3房)
 $1709万
 $22,197/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -39368,7 +39368,7 @@
           <t>E | 474呎 (2房)
 $1053万
 $22,217/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -39376,7 +39376,7 @@
           <t>F | 537呎 (2房)
 $1190万
 $22,164/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -39384,7 +39384,7 @@
           <t>G | 485呎 (2房)
 $1023万
 $21,101/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -39392,7 +39392,7 @@
           <t>H | 489呎 (2房)
 $1083万
 $22,145/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -39400,7 +39400,7 @@
           <t>J | 775呎 (3房)
 $1784万
 $23,015/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -39415,7 +39415,7 @@
           <t>A | 802呎 (3房)
 $1750万
 $21,827/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -39423,7 +39423,7 @@
           <t>B | 781呎 (3房)
 $1808万
 $23,156/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39431,7 +39431,7 @@
           <t>C | 509呎 (2房)
 $1164万
 $22,872/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -39439,7 +39439,7 @@
           <t>D | 770呎 (3房)
 $1700万
 $22,075/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -39447,7 +39447,7 @@
           <t>E | 474呎 (2房)
 $1017万
 $21,451/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -39455,7 +39455,7 @@
           <t>F | 537呎 (2房)
 $1184万
 $22,043/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -39463,7 +39463,7 @@
           <t>G | 485呎 (2房)
 $1005万
 $20,730/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -39471,7 +39471,7 @@
           <t>H | 489呎 (2房)
 $1046万
 $21,401/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -39479,7 +39479,7 @@
           <t>J | 775呎 (3房)
 $1775万
 $22,901/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -39494,7 +39494,7 @@
           <t>A | 802呎 (3房)
 $1692万
 $21,094/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -39502,7 +39502,7 @@
           <t>B | 781呎 (3房)
 $1799万
 $23,029/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -39510,7 +39510,7 @@
           <t>C | 509呎 (2房)
 $1125万
 $22,104/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -39518,7 +39518,7 @@
           <t>D | 770呎 (3房)
 $1690万
 $21,955/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -39526,7 +39526,7 @@
           <t>E | 474呎 (2房)
 $1010万
 $21,312/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -39534,7 +39534,7 @@
           <t>F | 537呎 (2房)
 $1144万
 $21,304/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -39542,7 +39542,7 @@
           <t>G | 485呎 (2房)
 $985万
 $20,313/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>H | 489呎 (2房)
 $1071万
 $21,904/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>J | 775呎 (3房)
 $1766万
 $22,788/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -39573,7 +39573,7 @@
           <t>A | 802呎 (3房)
 $1731万
 $21,587/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -39581,7 +39581,7 @@
           <t>B | 781呎 (3房)
 $1738万
 $22,256/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39589,7 +39589,7 @@
           <t>C | 509呎 (2房)
 $1152万
 $22,623/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -39597,7 +39597,7 @@
           <t>D | 770呎 (3房)
 $1681万
 $21,834/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>E | 474呎 (2房)
 $998万
 $21,061/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>F | 537呎 (2房)
 $1171万
 $21,804/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>G | 485呎 (2房)
 $968万
 $19,955/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -39629,7 +39629,7 @@
           <t>H | 489呎 (2房)
 $1035万
 $21,170/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>J | 775呎 (3房)
 $1708万
 $22,041/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -39652,7 +39652,7 @@
           <t>A | 802呎 (3房)
 $1676万
 $20,899/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39660,7 +39660,7 @@
           <t>B | 781呎 (3房)
 $1782万
 $22,817/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39668,7 +39668,7 @@
           <t>C | 509呎 (2房)
 $1147万
 $22,536/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 770呎 (3房)
 $1675万
 $21,753/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 474呎 (2房)
 $994万
 $20,975/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 537呎 (2房)
 $1133万
 $21,101/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -39700,7 +39700,7 @@
           <t>G | 485呎 (2房)
 $992万
 $20,454/呎
-(25年-01月-16日)</t>
+(25年-01月-17日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -39708,7 +39708,7 @@
           <t>H | 489呎 (2房)
 $1037万
 $21,207/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -39716,7 +39716,7 @@
           <t>J | 775呎 (3房)
 $1751万
 $22,591/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -39731,7 +39731,7 @@
           <t>A | 802呎 (3房)
 $1718万
 $21,424/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39739,7 +39739,7 @@
           <t>B | 781呎 (3房)
 $1725万
 $22,090/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>C | 509呎 (2房)
 $1110万
 $21,817/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -39755,7 +39755,7 @@
           <t>D | 770呎 (3房)
 $1600万
 $20,783/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -39763,7 +39763,7 @@
           <t>E | 474呎 (2房)
 $1019万
 $21,500/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -39771,7 +39771,7 @@
           <t>F | 537呎 (2房)
 $1162万
 $21,629/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -39779,7 +39779,7 @@
           <t>G | 485呎 (2房)
 $988万
 $20,371/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -39787,7 +39787,7 @@
           <t>H | 489呎 (2房)
 $1057万
 $21,609/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -39795,7 +39795,7 @@
           <t>J | 775呎 (3房)
 $1694万
 $21,865/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
           <t>A | 802呎 (3房)
 $1712万
 $21,344/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39818,7 +39818,7 @@
           <t>B | 781呎 (3房)
 $1769万
 $22,645/呎
-(24年-12月-04日)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39826,7 +39826,7 @@
           <t>C | 509呎 (2房)
 $1138万
 $22,365/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -39834,7 +39834,7 @@
           <t>D | 770呎 (3房)
 $1640万
 $21,305/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -39842,7 +39842,7 @@
           <t>E | 474呎 (2房)
 $986万
 $20,808/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -39850,7 +39850,7 @@
           <t>F | 537呎 (2房)
 $1124万
 $20,935/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -39858,7 +39858,7 @@
           <t>G | 485呎 (2房)
 $956万
 $19,718/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -39866,7 +39866,7 @@
           <t>H | 489呎 (2房)
 $1052万
 $21,524/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -39874,7 +39874,7 @@
           <t>J | 775呎 (3房)
 $1688万
 $21,778/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -39889,7 +39889,7 @@
           <t>A | 802呎 (3房)
 $1705万
 $21,263/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39897,7 +39897,7 @@
           <t>B | 781呎 (3房)
 $1712万
 $21,922/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39905,7 +39905,7 @@
           <t>C | 509呎 (2房)
 $1102万
 $21,652/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -39913,7 +39913,7 @@
           <t>D | 770呎 (3房)
 $1634万
 $21,226/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -39921,7 +39921,7 @@
           <t>E | 474呎 (2房)
 $982万
 $20,726/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -39929,7 +39929,7 @@
           <t>F | 537呎 (2房)
 $1120万
 $20,851/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -39937,7 +39937,7 @@
           <t>G | 485呎 (2房)
 $952万
 $19,639/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -39945,7 +39945,7 @@
           <t>H | 489呎 (2房)
 $1019万
 $20,834/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -39953,7 +39953,7 @@
           <t>J | 775呎 (3房)
 $1730万
 $22,321/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -39968,7 +39968,7 @@
           <t>A | 802呎 (3房)
 $1699万
 $21,182/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39976,7 +39976,7 @@
           <t>B | 781呎 (3房)
 $1755万
 $22,474/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39984,7 +39984,7 @@
           <t>C | 509呎 (2房)
 $1130万
 $22,196/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -39992,7 +39992,7 @@
           <t>D | 770呎 (3房)
 $1628万
 $21,144/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -40000,7 +40000,7 @@
           <t>E | 474呎 (2房)
 $978万
 $20,641/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -40008,7 +40008,7 @@
           <t>F | 537呎 (2房)
 $1148万
 $21,374/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -40016,7 +40016,7 @@
           <t>G | 485呎 (2房)
 $976万
 $20,128/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -40024,7 +40024,7 @@
           <t>H | 489呎 (2房)
 $1044万
 $21,352/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -40032,7 +40032,7 @@
           <t>J | 775呎 (3房)
 $1723万
 $22,232/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -40047,7 +40047,7 @@
           <t>A | 802呎 (3房)
 $1692万
 $21,097/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40055,7 +40055,7 @@
           <t>B | 781呎 (3房)
 $1699万
 $21,753/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40063,7 +40063,7 @@
           <t>C | 509呎 (2房)
 $1125万
 $22,108/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -40071,7 +40071,7 @@
           <t>D | 770呎 (3房)
 $1643万
 $21,340/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -40079,7 +40079,7 @@
           <t>E | 474呎 (2房)
 $980万
 $20,667/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -40087,7 +40087,7 @@
           <t>F | 537呎 (2房)
 $1143万
 $21,277/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -40095,7 +40095,7 @@
           <t>G | 485呎 (2房)
 $944万
 $19,474/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -40103,7 +40103,7 @@
           <t>H | 489呎 (2房)
 $1010万
 $20,658/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -40111,7 +40111,7 @@
           <t>J | 775呎 (3房)
 $1667万
 $21,514/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -40126,7 +40126,7 @@
           <t>A | 802呎 (3房)
 $1630万
 $20,319/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40134,7 +40134,7 @@
           <t>B | 781呎 (3房)
 $1733万
 $22,186/呎
-(25年-01月-21日)</t>
+(25年-01月-22日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -40142,7 +40142,7 @@
           <t>C | 509呎 (2房)
 $1115万
 $21,912/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -40150,7 +40150,7 @@
           <t>D | 770呎 (3房)
 $1628万
 $21,149/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -40158,7 +40158,7 @@
           <t>E | 474呎 (2房)
 $998万
 $21,049/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -40166,7 +40166,7 @@
           <t>F | 537呎 (2房)
 $1105万
 $20,585/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -40174,7 +40174,7 @@
           <t>G | 485呎 (2房)
 $968万
 $19,951/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -40182,7 +40182,7 @@
           <t>H | 489呎 (2房)
 $1035万
 $21,162/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -40190,7 +40190,7 @@
           <t>J | 775呎 (3房)
 $1709万
 $22,046/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -40205,7 +40205,7 @@
           <t>A | 802呎 (3房)
 $1670万
 $20,820/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40213,7 +40213,7 @@
           <t>B | 781呎 (3房)
 $1676万
 $21,466/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40221,7 +40221,7 @@
           <t>C | 509呎 (2房)
 $1111万
 $21,819/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -40229,7 +40229,7 @@
           <t>D | 770呎 (3房)
 $1622万
 $21,058/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -40237,7 +40237,7 @@
           <t>E | 474呎 (2房)
 $965万
 $20,361/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -40245,7 +40245,7 @@
           <t>F | 537呎 (2房)
 $1132万
 $21,088/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -40253,7 +40253,7 @@
           <t>G | 485呎 (2房)
 $942万
 $19,412/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -40261,7 +40261,7 @@
           <t>H | 489呎 (2房)
 $1030万
 $21,067/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -40269,7 +40269,7 @@
           <t>J | 775呎 (3房)
 $1701万
 $21,954/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -40284,7 +40284,7 @@
           <t>A | 802呎 (3房)
 $1616万
 $20,146/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40292,7 +40292,7 @@
           <t>B | 781呎 (3房)
 $1718万
 $21,996/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -40300,7 +40300,7 @@
           <t>C | 509呎 (2房)
 $1106万
 $21,725/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -40308,7 +40308,7 @@
           <t>D | 770呎 (3房)
 $1615万
 $20,969/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -40316,7 +40316,7 @@
           <t>E | 474呎 (2房)
 $989万
 $20,857/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -40324,7 +40324,7 @@
           <t>F | 537呎 (2房)
 $1123万
 $20,920/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -40332,7 +40332,7 @@
           <t>G | 485呎 (2房)
 $931万
 $19,200/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -40340,7 +40340,7 @@
           <t>H | 489呎 (2房)
 $1026万
 $20,971/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -40348,7 +40348,7 @@
           <t>J | 775呎 (3房)
 $1646万
 $21,245/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -40363,7 +40363,7 @@
           <t>A | 802呎 (3房)
 $1609万
 $20,060/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -40371,7 +40371,7 @@
           <t>B | 781呎 (3房)
 $1710万
 $21,900/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -40379,7 +40379,7 @@
           <t>C | 509呎 (2房)
 $1101万
 $21,631/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -40387,7 +40387,7 @@
           <t>D | 770呎 (3房)
 $1608万
 $20,878/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -40395,7 +40395,7 @@
           <t>E | 474呎 (2房)
 $984万
 $20,762/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -40403,7 +40403,7 @@
           <t>F | 537呎 (2房)
 $1083万
 $20,168/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -40411,7 +40411,7 @@
           <t>G | 485呎 (2房)
 $953万
 $19,654/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -40419,7 +40419,7 @@
           <t>H | 489呎 (2房)
 $992万
 $20,288/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -40427,7 +40427,7 @@
           <t>J | 775呎 (3房)
 $1640万
 $21,156/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -40442,7 +40442,7 @@
           <t>A | 802呎 (3房)
 $1641万
 $20,459/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -40450,7 +40450,7 @@
           <t>B | 781呎 (3房)
 $1695万
 $21,706/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -40458,7 +40458,7 @@
           <t>C | 509呎 (2房)
 $1060万
 $20,835/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -40466,7 +40466,7 @@
           <t>D | 770呎 (3房)
 $1548万
 $20,108/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -40474,7 +40474,7 @@
           <t>E | 474呎 (2房)
 $948万
 $20,004/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -40482,7 +40482,7 @@
           <t>F | 537呎 (2房)
 $1074万
 $19,998/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -40490,7 +40490,7 @@
           <t>G | 485呎 (2房)
 $921万
 $18,998/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -40498,7 +40498,7 @@
           <t>H | 489呎 (2房)
 $988万
 $20,198/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -40506,7 +40506,7 @@
           <t>J | 775呎 (3房)
 $1676万
 $21,619/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -40521,7 +40521,7 @@
           <t>A | 802呎 (3房)
 $1611万
 $20,087/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -40529,7 +40529,7 @@
           <t>B | 781呎 (3房)
 $1676万
 $21,465/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -40537,7 +40537,7 @@
           <t>C | 509呎 (2房)
 $1085万
 $21,322/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -40545,7 +40545,7 @@
           <t>D | 770呎 (3房)
 $1564万
 $20,313/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -40553,7 +40553,7 @@
           <t>E | 474呎 (2房)
 $960万
 $20,262/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -40561,7 +40561,7 @@
           <t>F | 537呎 (2房)
 $1138万
 $21,188/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -40569,7 +40569,7 @@
           <t>G | 485呎 (2房)
 $940万
 $19,373/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -40577,7 +40577,7 @@
           <t>H | 489呎 (2房)
 $1082万
 $22,127/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="J35" s="20" t="inlineStr">
@@ -40585,7 +40585,7 @@
           <t>J | 775呎 (3房)
 $1604万
 $20,699/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
     </row>
